--- a/Treinamento/Cópia de GeraBlocoBCadastroCorretor.xlsx
+++ b/Treinamento/Cópia de GeraBlocoBCadastroCorretor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE00572-R0407280\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF202EFD-DFC9-4FEE-A9E0-740801F306F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92843E1-C87E-4D8E-84C6-11952CC86B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,7 +149,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -162,6 +162,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{9C500936-D842-4095-84AB-BAB79AFDFC42}"/>
@@ -505,203 +511,183 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>4034862</v>
+      <c r="A2" s="9">
+        <v>4034858</v>
       </c>
       <c r="B2" s="4"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>4034871</v>
+      <c r="A3" s="9">
+        <v>4034863</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>4034872</v>
+      <c r="A4" s="9">
+        <v>4034859</v>
       </c>
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>4034867</v>
+      <c r="A5" s="8">
+        <v>4034860</v>
       </c>
       <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>4034870</v>
+      <c r="A6" s="8">
+        <v>4034861</v>
       </c>
       <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>4034869</v>
+      <c r="A7" s="8">
+        <v>4034873</v>
       </c>
       <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>4034866</v>
+      <c r="A8" s="8">
+        <v>4034864</v>
       </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>4034855</v>
+      <c r="A9" s="8">
+        <v>4034865</v>
       </c>
       <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>4034856</v>
+      <c r="A10" s="8">
+        <v>4034891</v>
       </c>
       <c r="B10" s="4"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>4034857</v>
+      <c r="A11" s="8">
+        <v>4034868</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>4034858</v>
+      <c r="A12" s="8">
+        <v>4034874</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>4034863</v>
+      <c r="A13" s="8">
+        <v>4034875</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>4034859</v>
+      <c r="A14" s="8">
+        <v>4034876</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>4034860</v>
+      <c r="A15" s="8">
+        <v>4034881</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>4034861</v>
+      <c r="A16" s="8">
+        <v>4034882</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>4034873</v>
+      <c r="A17" s="8">
+        <v>4034880</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>4034864</v>
+      <c r="A18" s="8">
+        <v>4034877</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>4034865</v>
+      <c r="A19" s="8">
+        <v>4034878</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>4034891</v>
+      <c r="A20" s="8">
+        <v>4034887</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>4034868</v>
+      <c r="A21" s="8">
+        <v>4034879</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>4034874</v>
+      <c r="A22" s="8">
+        <v>4034892</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>4034875</v>
+      <c r="A23" s="8">
+        <v>4034889</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>4034876</v>
+      <c r="A24" s="8">
+        <v>4034888</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>4034881</v>
+      <c r="A25" s="8">
+        <v>4034883</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>4034882</v>
+      <c r="A26" s="8">
+        <v>4034884</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>4034880</v>
+      <c r="A27" s="8">
+        <v>4034885</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>4034877</v>
+      <c r="A28" s="8">
+        <v>4034886</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>4034878</v>
+      <c r="A29" s="8">
+        <v>4034890</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>4034887</v>
-      </c>
+      <c r="A30" s="7"/>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
-        <v>4034879</v>
-      </c>
+      <c r="A31" s="7"/>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
-        <v>4034892</v>
-      </c>
+      <c r="A32" s="7"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
-        <v>4034889</v>
-      </c>
+      <c r="A33" s="7"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
-        <v>4034888</v>
-      </c>
+      <c r="A34" s="7"/>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
-        <v>4034883</v>
-      </c>
+      <c r="A35" s="7"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
-        <v>4034884</v>
-      </c>
+      <c r="A36" s="7"/>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
-        <v>4034885</v>
-      </c>
+      <c r="A37" s="7"/>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
-        <v>4034886</v>
-      </c>
+      <c r="A38" s="7"/>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
-        <v>4034890</v>
-      </c>
+      <c r="A39" s="7"/>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="7"/>
@@ -1048,31 +1034,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>